--- a/data/colleges_final/sepehr_colleges_links.xlsx
+++ b/data/colleges_final/sepehr_colleges_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sepehrakbari/Projects/enrollment-cliff/data/colleges_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E147B63C-B766-E346-9742-0A0953ED8D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1AB38-A6D9-8B45-B625-C57AB9B8CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="166">
   <si>
     <t>index</t>
   </si>
@@ -52,12 +52,6 @@
     <t>New York</t>
   </si>
   <si>
-    <t>American University of Puerto Rico</t>
-  </si>
-  <si>
-    <t>Puerto Rico</t>
-  </si>
-  <si>
     <t>Ancilla College</t>
   </si>
   <si>
@@ -328,24 +322,15 @@
     <t>links</t>
   </si>
   <si>
-    <t>https://www.cnn.com/2023/08/02/us/west-virginia-alderson-broaddus-university-closes-students</t>
-  </si>
-  <si>
     <t>https://www.highereddive.com/news/alliance-university-to-close-in-august/685035/</t>
   </si>
   <si>
     <t>https://www.inkfreenews.com/2020/08/28/ancilla-college-marian-university-announce-merger-new-name/</t>
   </si>
   <si>
-    <t>https://www.nbcnewyork.com/news/good-news/small-nj-college-gets-saved-from-closing-thanks-to-unusual-partnership/3623834/</t>
-  </si>
-  <si>
     <t>https://apnews.com/general-news-f28092c26214a68bd470db9dd705a003#:~:text=(AP)%20%E2%80%94%20Becker%20College%20in,posted%20on%20its%20website%20Monday.</t>
   </si>
   <si>
-    <t>https://www.limaohio.com/top-stories/2025/03/15/not-a-do-or-die-moment-despite-failed-merger-bluffton-university-remains-financially-stable/</t>
-  </si>
-  <si>
     <t>https://apnews.com/article/cabrini-university-closing-villanova-01834d1e3e89cedfabf15f7a03d417b3#:~:text=RADNOR%2C%20Pa.,Roman%20Catholic%20university%20is%20located.</t>
   </si>
   <si>
@@ -373,9 +358,6 @@
     <t>https://www.highereddive.com/news/hodges-university-to-close-by-august-2024/692078/#:~:text=from%20your%20inbox.-,Hodges%20University%20to%20close%20by%20August%202024,enrollment%20challenges%20and%20financial%20difficulties.</t>
   </si>
   <si>
-    <t>https://www.wearegreenbay.com/news/local-news/manitowocs-holy-family-college-to-cease-operations-after-summer-term/</t>
-  </si>
-  <si>
     <t>https://www.highereddive.com/news/holy-names-university-closing-may-no-merger/639212/</t>
   </si>
   <si>
@@ -455,6 +437,87 @@
   </si>
   <si>
     <t>https://www.carsonnow.org/07/06/2022/inclines-sierra-nevada-university-officially-becomes-university-nevada-reno-lake-ta#:~:text=Sierra%20Nevada%20University%20officially%20becomes%20University%20of,Lake%20Tahoe%20following%20merger%20%2D%20Carson%20Now.&amp;text=As%20of%20July%2C%20the%20Incline%20Village%20college%2C,University%20of%20Nevada%2C%20Reno%20at%20Lake%20Tahoe.</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/saint-augustines-loses-accreditation-appeal/741974/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/st-johns-university-to-close-staten-island-campus-in-spring-2024/629675/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/meet-a-president-guiding-the-merger-of-2-missouri-religious-colleges/629463/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/the-college-of-saint-rose-close-spring-2024-end-of-academic-year/701349/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/heres-how-saint-josephs-closed-its-university-of-the-sciences-acquisition/624787/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/columbus-franklin-and-urbana-universities-merge/257181/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/uw-oshkosh-cuts-workforce-by-more-than-200-as-budget-crisis-unfolds/696898/</t>
+  </si>
+  <si>
+    <t>https://www.wpr.org/education/higher-education/uw-green-bay-ending-in-person-classes-in-marinette-county</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/university-wisconsin-branch-campus-merger-consolidation-technical-college/653955/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/wave-leadership-college-a-nonprofit-religious-institution-closes/627066/</t>
+  </si>
+  <si>
+    <t>https://www.axios.com/local/san-diego/2024/05/01/urban-development-trendsetter-woodbury-school-architecture-closing</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/oak-point-university-to-close-abruptly-april-healthcare-chicago/711797/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/birmingham-southern-to-shutter-may-31-alabama/711439/</t>
+  </si>
+  <si>
+    <t>https://www.fox23.com/news/tcc-announces-upcoming-closure-of-owasso-campus/article_fd045594-ebc4-11ee-be89-47e517aff9b6.html</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/wells-college-closure-end-of-the-spring-term-semester-abrupt/714628/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/eastern-nazarene-college-in-massachusetts-to-close/719969/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/cox-college-closing-healthcare-alliance/692522/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/uw-platteville-to-cut-111-positions/697964/#:~:text=Last%20November%2C%20Universities%20of%20Wisconsin,the%20Richland%20campus%20would%20close.</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/notre-dame-of-maryland-university-to-acquire-Maryland-University-of-Integrative-Health/698227/</t>
+  </si>
+  <si>
+    <t>https://baptiststandard.com/news/texas/carroll-seminary-withdraws-from-abhe-accreditation/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/university-of-findlay-calls-off-merger-bluffton-university/741305/</t>
+  </si>
+  <si>
+    <t>https://www.jsonline.com/story/news/education/2020/05/15/wake-holy-family-college-closing-students-plan-transfer/5183921002/</t>
+  </si>
+  <si>
+    <t>https://whyy.org/articles/delaware-state-becomes-first-hbcu-to-acquire-another-school-with-takeover-of-wesley-college/</t>
+  </si>
+  <si>
+    <t>https://uwm.edu/news/uwm-at-waukesha-campus-to-close-in-2025-uwm-develops-university-center-with-wctc/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/alderson-broaddus-university-loses-state-operating-approval-portending-clo/689582/</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/months-after-plea-bloomfield-college-will-remain-open-with-help-from-montc/620943/</t>
+  </si>
+  <si>
+    <t>hed</t>
   </si>
 </sst>
 </file>
@@ -492,7 +555,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -508,12 +571,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,28 +603,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -872,19 +925,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" customWidth="1"/>
-    <col min="4" max="4" width="49.1640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="4" max="4" width="49.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -894,20 +947,23 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -917,20 +973,20 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2">
         <v>1871</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -940,1138 +996,1212 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3">
         <v>1882</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>241100</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4">
+        <v>497833</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="4">
-        <v>1963</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1937</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>497833</v>
+        <v>164720</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>1937</v>
-      </c>
-      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1784</v>
+      </c>
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2021</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>164720</v>
+        <v>183822</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6">
-        <v>1784</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6">
+        <v>1868</v>
+      </c>
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="G6">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>183822</v>
+        <v>201371</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7">
-        <v>1868</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7">
+        <v>1899</v>
+      </c>
+      <c r="G7" t="s">
         <v>17</v>
       </c>
-      <c r="G7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>201371</v>
+        <v>211352</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>107</v>
+      <c r="D8" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="E8">
-        <v>1899</v>
-      </c>
-      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1957</v>
+      </c>
+      <c r="G8" t="s">
         <v>19</v>
       </c>
-      <c r="G8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>211352</v>
+        <v>238430</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>108</v>
+      <c r="D9" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="E9">
-        <v>1957</v>
-      </c>
-      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1937</v>
+      </c>
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="G9">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>238430</v>
+        <v>189848</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10">
-        <v>1937</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10">
+      <c r="D10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10">
+        <v>1824</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10">
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>189848</v>
+        <v>201751</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11">
-        <v>1824</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11">
+        <v>1971</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11">
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>201751</v>
+        <v>459417</v>
       </c>
       <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12">
+        <v>1997</v>
+      </c>
+      <c r="G12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12">
-        <v>1971</v>
-      </c>
-      <c r="F12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12">
+      <c r="H12">
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>459417</v>
+        <v>190248</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13">
-        <v>1997</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="D13" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13">
+        <v>1881</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>190248</v>
+        <v>172440</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>113</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>1881</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1896</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>172440</v>
+        <v>177418</v>
       </c>
       <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15">
+        <v>1923</v>
+      </c>
+      <c r="G15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15">
-        <v>1896</v>
-      </c>
-      <c r="F15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>177418</v>
+        <v>367884</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16">
-        <v>1923</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D16" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16">
+        <v>1990</v>
+      </c>
+      <c r="G16" t="s">
         <v>31</v>
       </c>
-      <c r="G16">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>367884</v>
+        <v>239743</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>116</v>
+      <c r="D17" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="E17">
-        <v>1990</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1935</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>239743</v>
+        <v>115728</v>
       </c>
       <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18">
+        <v>1868</v>
+      </c>
+      <c r="G18" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18">
-        <v>1935</v>
-      </c>
-      <c r="F18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>115728</v>
+        <v>465812</v>
       </c>
       <c r="C19" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19">
-        <v>1868</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19">
+        <v>1978</v>
+      </c>
+      <c r="G19" t="s">
         <v>36</v>
       </c>
-      <c r="G19">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20">
-        <v>465812</v>
+        <v>151111</v>
       </c>
       <c r="C20" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20">
-        <v>1978</v>
-      </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="D20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20">
+        <v>1969</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>151111</v>
+        <v>153621</v>
       </c>
       <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21">
+        <v>1842</v>
+      </c>
+      <c r="G21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21">
-        <v>1969</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>153621</v>
+        <v>132879</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22">
-        <v>1842</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="D22" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22">
+        <v>1893</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23">
-        <v>132879</v>
+        <v>101541</v>
       </c>
       <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1838</v>
+      </c>
+      <c r="G23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23">
-        <v>1893</v>
-      </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24">
-        <v>101541</v>
+        <v>146667</v>
       </c>
       <c r="C24" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24">
-        <v>1838</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="D24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24">
+        <v>1944</v>
+      </c>
+      <c r="G24" t="s">
         <v>44</v>
       </c>
-      <c r="G24">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25">
-        <v>146667</v>
+        <v>146676</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25">
-        <v>1944</v>
-      </c>
-      <c r="F25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="D25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25">
+        <v>1865</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26">
-        <v>146676</v>
+        <v>146825</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>125</v>
+        <v>46</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="E26">
-        <v>1865</v>
-      </c>
-      <c r="F26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>1846</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27">
-        <v>146825</v>
+        <v>182917</v>
       </c>
       <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1973</v>
+      </c>
+      <c r="G27" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27">
-        <v>1846</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28">
-        <v>182917</v>
+        <v>230940</v>
       </c>
       <c r="C28" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>135</v>
+      <c r="D28" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="E28">
-        <v>1973</v>
-      </c>
-      <c r="F28" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>1946</v>
+      </c>
+      <c r="G28" t="s">
         <v>50</v>
       </c>
-      <c r="G28">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29">
-        <v>230940</v>
+        <v>220701</v>
       </c>
       <c r="C29" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>128</v>
+      <c r="D29" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="E29">
-        <v>1946</v>
-      </c>
-      <c r="F29" t="s">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1870</v>
+      </c>
+      <c r="G29" t="s">
         <v>52</v>
       </c>
-      <c r="G29">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30">
-        <v>220701</v>
+        <v>118541</v>
       </c>
       <c r="C30" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30">
-        <v>1870</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30">
+        <v>1932</v>
+      </c>
+      <c r="G30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31">
-        <v>118541</v>
+        <v>192925</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31">
-        <v>1932</v>
-      </c>
-      <c r="F31" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31">
+        <v>1937</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32">
-        <v>192925</v>
+        <v>118888</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E32">
-        <v>1937</v>
-      </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32">
+        <v>1852</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33">
-        <v>118888</v>
+        <v>209287</v>
       </c>
       <c r="C33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33">
+        <v>1936</v>
+      </c>
+      <c r="G33" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33">
-        <v>1852</v>
-      </c>
-      <c r="F33" t="s">
-        <v>36</v>
-      </c>
-      <c r="G33">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34">
-        <v>209287</v>
-      </c>
       <c r="C34" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>133</v>
+      <c r="D34" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="E34">
-        <v>1936</v>
-      </c>
-      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1945</v>
+      </c>
+      <c r="G34" t="s">
         <v>59</v>
       </c>
-      <c r="G34">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
+      <c r="B35">
+        <v>204468</v>
+      </c>
       <c r="C35" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E35">
-        <v>1945</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D35" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35">
+        <v>1922</v>
+      </c>
+      <c r="G35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36">
-        <v>204468</v>
+        <v>237640</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36">
-        <v>1922</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36">
+        <v>1960</v>
+      </c>
+      <c r="G36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37">
-        <v>237640</v>
+        <v>209603</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37">
-        <v>1960</v>
-      </c>
-      <c r="F37" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37">
+        <v>62</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37">
+        <v>1909</v>
+      </c>
+      <c r="G37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H37">
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38">
-        <v>209603</v>
+        <v>442356</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38">
-        <v>1909</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38">
+        <v>1903</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39">
-        <v>442356</v>
+        <v>167455</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>138</v>
+        <v>64</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="E39">
-        <v>1903</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1911</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40">
-        <v>167455</v>
+        <v>219295</v>
       </c>
       <c r="C40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40">
+        <v>1951</v>
+      </c>
+      <c r="G40" t="s">
         <v>66</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40">
-        <v>1911</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41">
-        <v>219295</v>
+        <v>486433</v>
       </c>
       <c r="C41" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41">
-        <v>1951</v>
-      </c>
-      <c r="F41" t="s">
-        <v>68</v>
-      </c>
-      <c r="G41">
+      <c r="D41" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F41">
+        <v>2003</v>
+      </c>
+      <c r="G41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41">
         <v>2023</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42">
-        <v>486433</v>
+        <v>214564</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42">
-        <v>2003</v>
-      </c>
-      <c r="F42" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42">
+        <v>1919</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43">
-        <v>214564</v>
+        <v>122454</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43">
-        <v>1919</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43">
+        <v>1871</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44">
-        <v>122454</v>
+        <v>182458</v>
       </c>
       <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1969</v>
+      </c>
+      <c r="G44" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44">
-        <v>1871</v>
-      </c>
-      <c r="F44" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44">
+      <c r="H44">
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45">
-        <v>182458</v>
+        <v>148876</v>
       </c>
       <c r="C45" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E45">
-        <v>1969</v>
-      </c>
-      <c r="F45" t="s">
-        <v>73</v>
-      </c>
-      <c r="G45">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D45" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45">
+        <v>1980</v>
+      </c>
+      <c r="G45" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46">
-        <v>148876</v>
+        <v>19580901</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46">
-        <v>1980</v>
-      </c>
-      <c r="F46" t="s">
-        <v>46</v>
-      </c>
-      <c r="G46">
+        <v>73</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46">
+        <v>1933</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46">
         <v>2024</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47">
-        <v>19580901</v>
+        <v>179256</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47">
-        <v>1933</v>
-      </c>
-      <c r="F47" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47">
+        <v>1956</v>
+      </c>
+      <c r="G47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48">
-        <v>179256</v>
+        <v>195234</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48">
-        <v>1956</v>
-      </c>
-      <c r="F48" t="s">
-        <v>31</v>
-      </c>
-      <c r="G48">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48">
+        <v>1920</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49">
-        <v>195234</v>
+        <v>215132</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49">
-        <v>1920</v>
-      </c>
-      <c r="F49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G49">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F49">
+        <v>1821</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50">
-        <v>215132</v>
-      </c>
       <c r="C50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50">
-        <v>1821</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F50">
+        <v>1850</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
+      <c r="B51">
+        <v>240365</v>
+      </c>
       <c r="C51" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51">
-        <v>1850</v>
-      </c>
-      <c r="F51" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F51">
+        <v>1968</v>
+      </c>
+      <c r="G51" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52">
-        <v>240365</v>
+        <v>240277</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="E52">
-        <v>1968</v>
-      </c>
-      <c r="F52" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>1935</v>
+      </c>
+      <c r="G52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52">
         <v>2024</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53">
-        <v>240277</v>
+        <v>240453</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="E53">
-        <v>1935</v>
-      </c>
-      <c r="F53" t="s">
-        <v>23</v>
-      </c>
-      <c r="G53">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>1966</v>
+      </c>
+      <c r="G53" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2079,278 +2209,309 @@
         <v>240453</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54">
-        <v>1966</v>
-      </c>
-      <c r="F54" t="s">
-        <v>23</v>
-      </c>
-      <c r="G54">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54">
+        <v>1968</v>
+      </c>
+      <c r="G54" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55">
-        <v>240453</v>
-      </c>
       <c r="C55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F55">
+        <v>1999</v>
+      </c>
+      <c r="G55" t="s">
         <v>83</v>
       </c>
-      <c r="E55">
-        <v>1968</v>
-      </c>
-      <c r="F55" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
+      <c r="B56">
+        <v>131098</v>
+      </c>
       <c r="C56" t="s">
         <v>84</v>
       </c>
+      <c r="D56" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="E56">
-        <v>1999</v>
-      </c>
-      <c r="F56" t="s">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1873</v>
+      </c>
+      <c r="G56" t="s">
         <v>85</v>
       </c>
-      <c r="G56">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57">
-        <v>131098</v>
+        <v>125897</v>
       </c>
       <c r="C57" t="s">
         <v>86</v>
       </c>
+      <c r="D57" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="E57">
-        <v>1873</v>
-      </c>
-      <c r="F57" t="s">
-        <v>87</v>
-      </c>
-      <c r="G57">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>1884</v>
+      </c>
+      <c r="G57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58">
-        <v>125897</v>
+        <v>149763</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58">
-        <v>1884</v>
-      </c>
-      <c r="F58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58">
+        <v>87</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F58">
+        <v>1914</v>
+      </c>
+      <c r="G58" t="s">
+        <v>44</v>
+      </c>
+      <c r="H58">
         <v>2024</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59">
-        <v>149763</v>
+        <v>100937</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59">
-        <v>1914</v>
-      </c>
-      <c r="F59" t="s">
-        <v>46</v>
-      </c>
-      <c r="G59">
+        <v>88</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F59">
+        <v>1918</v>
+      </c>
+      <c r="G59" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59">
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60">
-        <v>100937</v>
+        <v>207935</v>
       </c>
       <c r="C60" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1970</v>
+      </c>
+      <c r="G60" t="s">
         <v>90</v>
       </c>
-      <c r="E60">
-        <v>1918</v>
-      </c>
-      <c r="F60" t="s">
-        <v>44</v>
-      </c>
-      <c r="G60">
+      <c r="H60">
         <v>2024</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61">
-        <v>207935</v>
+        <v>197230</v>
       </c>
       <c r="C61" t="s">
         <v>91</v>
       </c>
-      <c r="E61">
-        <v>1970</v>
-      </c>
-      <c r="F61" t="s">
-        <v>92</v>
-      </c>
-      <c r="G61">
+      <c r="D61" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61">
+        <v>1868</v>
+      </c>
+      <c r="G61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61">
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62">
-        <v>197230</v>
+        <v>165644</v>
       </c>
       <c r="C62" t="s">
-        <v>93</v>
-      </c>
-      <c r="E62">
-        <v>1868</v>
-      </c>
-      <c r="F62" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62">
+        <v>92</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F62">
+        <v>1900</v>
+      </c>
+      <c r="G62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62">
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63">
-        <v>165644</v>
+        <v>176770</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63">
-        <v>1900</v>
-      </c>
-      <c r="F63" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F63">
+        <v>1907</v>
+      </c>
+      <c r="G63" t="s">
+        <v>29</v>
+      </c>
+      <c r="H63">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64">
-        <v>176770</v>
+        <v>240462</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
-      </c>
-      <c r="E64">
-        <v>1907</v>
-      </c>
-      <c r="F64" t="s">
-        <v>31</v>
-      </c>
-      <c r="G64">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F64">
+        <v>1967</v>
+      </c>
+      <c r="G64" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65">
-        <v>240462</v>
+        <v>164085</v>
       </c>
       <c r="C65" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F65">
+        <v>1974</v>
+      </c>
+      <c r="G65" t="s">
         <v>96</v>
       </c>
-      <c r="E65">
-        <v>1967</v>
-      </c>
-      <c r="F65" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66">
-        <v>164085</v>
-      </c>
       <c r="C66" t="s">
         <v>97</v>
       </c>
+      <c r="D66" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="E66">
-        <v>1974</v>
-      </c>
-      <c r="F66" t="s">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>2004</v>
+      </c>
+      <c r="G66" t="s">
         <v>98</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>65</v>
-      </c>
-      <c r="C67" t="s">
-        <v>99</v>
-      </c>
-      <c r="E67">
-        <v>2004</v>
-      </c>
-      <c r="F67" t="s">
-        <v>100</v>
-      </c>
-      <c r="G67">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D68" s="8"/>
+    <row r="67" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D67" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" location=":~:text=(AP)%20%E2%80%94%20Becker%20College%20in,posted%20on%20its%20website%20Monday." xr:uid="{12E03591-513F-7B40-8627-3F935F2822DB}"/>
+    <hyperlink ref="D5" r:id="rId1" location=":~:text=(AP)%20%E2%80%94%20Becker%20College%20in,posted%20on%20its%20website%20Monday." xr:uid="{12E03591-513F-7B40-8627-3F935F2822DB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/colleges_final/sepehr_colleges_links.xlsx
+++ b/data/colleges_final/sepehr_colleges_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sepehrakbari/Projects/enrollment-cliff/data/colleges_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1AB38-A6D9-8B45-B625-C57AB9B8CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5080D21E-831A-8B44-AF7A-51E8A3170578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -334,9 +334,6 @@
     <t>https://apnews.com/article/cabrini-university-closing-villanova-01834d1e3e89cedfabf15f7a03d417b3#:~:text=RADNOR%2C%20Pa.,Roman%20Catholic%20university%20is%20located.</t>
   </si>
   <si>
-    <t>https://www.milwaukeemag.com/why-did-cardinal-stritch-university-close-after-86-years/</t>
-  </si>
-  <si>
     <t>https://www.highereddive.com/news/cazenovia-college-says-it-will-close-in-spring-2023-citing-financial-stres/638255/</t>
   </si>
   <si>
@@ -518,6 +515,9 @@
   </si>
   <si>
     <t>hed</t>
+  </si>
+  <si>
+    <t>https://www.highereddive.com/news/cardinal-stritch-university-campus-purchased-for-24m/689752/</t>
   </si>
 </sst>
 </file>
@@ -951,7 +951,7 @@
         <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -974,7 +974,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F2">
         <v>1871</v>
@@ -1072,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F6">
         <v>1868</v>
@@ -1095,7 +1095,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F7">
         <v>1899</v>
@@ -1117,7 +1117,7 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>103</v>
       </c>
       <c r="E8">
@@ -1143,11 +1143,8 @@
       <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="D9" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="F9">
         <v>1937</v>
@@ -1170,7 +1167,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10">
         <v>1824</v>
@@ -1193,7 +1190,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11">
         <v>1971</v>
@@ -1216,7 +1213,7 @@
         <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F12">
         <v>1997</v>
@@ -1239,7 +1236,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F13">
         <v>1881</v>
@@ -1262,7 +1259,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1288,7 +1285,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F15">
         <v>1923</v>
@@ -1311,7 +1308,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F16">
         <v>1990</v>
@@ -1334,7 +1331,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1360,7 +1357,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18">
         <v>1868</v>
@@ -1383,7 +1380,7 @@
         <v>35</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F19">
         <v>1978</v>
@@ -1406,7 +1403,7 @@
         <v>37</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F20">
         <v>1969</v>
@@ -1429,7 +1426,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F21">
         <v>1842</v>
@@ -1452,7 +1449,7 @@
         <v>40</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F22">
         <v>1893</v>
@@ -1474,8 +1471,8 @@
       <c r="C23" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>117</v>
+      <c r="D23" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1501,7 +1498,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F24">
         <v>1944</v>
@@ -1524,7 +1521,7 @@
         <v>45</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F25">
         <v>1865</v>
@@ -1547,7 +1544,7 @@
         <v>46</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1573,7 +1570,7 @@
         <v>47</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1598,8 +1595,8 @@
       <c r="C28" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>122</v>
+      <c r="D28" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1625,7 +1622,7 @@
         <v>51</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1651,7 +1648,7 @@
         <v>53</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F30">
         <v>1932</v>
@@ -1674,7 +1671,7 @@
         <v>54</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31">
         <v>1937</v>
@@ -1697,7 +1694,7 @@
         <v>55</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F32">
         <v>1852</v>
@@ -1720,7 +1717,7 @@
         <v>56</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33">
         <v>1936</v>
@@ -1740,7 +1737,7 @@
         <v>58</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1766,7 +1763,7 @@
         <v>60</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F35">
         <v>1922</v>
@@ -1789,7 +1786,7 @@
         <v>61</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F36">
         <v>1960</v>
@@ -1812,7 +1809,7 @@
         <v>62</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F37">
         <v>1909</v>
@@ -1835,7 +1832,7 @@
         <v>63</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F38">
         <v>1903</v>
@@ -1857,8 +1854,8 @@
       <c r="C39" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>133</v>
+      <c r="D39" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1884,7 +1881,7 @@
         <v>65</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F40">
         <v>1951</v>
@@ -1907,7 +1904,7 @@
         <v>67</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41">
         <v>2003</v>
@@ -1930,7 +1927,7 @@
         <v>68</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F42">
         <v>1919</v>
@@ -1953,7 +1950,7 @@
         <v>69</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F43">
         <v>1871</v>
@@ -1976,7 +1973,7 @@
         <v>70</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2002,7 +1999,7 @@
         <v>72</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F45">
         <v>1980</v>
@@ -2025,7 +2022,7 @@
         <v>73</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F46">
         <v>1933</v>
@@ -2048,7 +2045,7 @@
         <v>74</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F47">
         <v>1956</v>
@@ -2071,7 +2068,7 @@
         <v>75</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F48">
         <v>1920</v>
@@ -2094,7 +2091,7 @@
         <v>76</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F49">
         <v>1821</v>
@@ -2114,7 +2111,7 @@
         <v>77</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F50">
         <v>1850</v>
@@ -2137,7 +2134,7 @@
         <v>78</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F51">
         <v>1968</v>
@@ -2160,7 +2157,7 @@
         <v>79</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2186,7 +2183,7 @@
         <v>80</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2212,7 +2209,7 @@
         <v>81</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F54">
         <v>1968</v>
@@ -2232,7 +2229,7 @@
         <v>82</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F55">
         <v>1999</v>
@@ -2255,7 +2252,7 @@
         <v>84</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2280,8 +2277,8 @@
       <c r="C57" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>149</v>
+      <c r="D57" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2307,7 +2304,7 @@
         <v>87</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F58">
         <v>1914</v>
@@ -2330,7 +2327,7 @@
         <v>88</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F59">
         <v>1918</v>
@@ -2353,7 +2350,7 @@
         <v>89</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2379,7 +2376,7 @@
         <v>91</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F61">
         <v>1868</v>
@@ -2402,7 +2399,7 @@
         <v>92</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F62">
         <v>1900</v>
@@ -2425,7 +2422,7 @@
         <v>93</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F63">
         <v>1907</v>
@@ -2448,7 +2445,7 @@
         <v>94</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64">
         <v>1967</v>
@@ -2471,7 +2468,7 @@
         <v>95</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F65">
         <v>1974</v>
@@ -2490,8 +2487,8 @@
       <c r="C66" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>158</v>
+      <c r="D66" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2512,6 +2509,13 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" location=":~:text=(AP)%20%E2%80%94%20Becker%20College%20in,posted%20on%20its%20website%20Monday." xr:uid="{12E03591-513F-7B40-8627-3F935F2822DB}"/>
+    <hyperlink ref="D8" r:id="rId2" location=":~:text=RADNOR%2C%20Pa.,Roman%20Catholic%20university%20is%20located." xr:uid="{8F3A0408-624E-164D-BEC7-983E388DB92D}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{AB2CFD3E-07C4-6F44-A63E-242B08043C2F}"/>
+    <hyperlink ref="D23" r:id="rId4" xr:uid="{4E370BEB-3B34-1649-B7C6-F348E816861F}"/>
+    <hyperlink ref="D28" r:id="rId5" xr:uid="{0D1D8957-1EAB-FE4D-93AF-C9FD68B74176}"/>
+    <hyperlink ref="D39" r:id="rId6" xr:uid="{388BADFA-5DBA-CA42-A90F-5078C0C654E1}"/>
+    <hyperlink ref="D57" r:id="rId7" xr:uid="{7451D030-828E-7642-A52D-60E3E721DA34}"/>
+    <hyperlink ref="D66" r:id="rId8" xr:uid="{228052F7-9D77-5440-875A-0C28D30141A5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
